--- a/excel/usuarios_funcionalidades.xlsx
+++ b/excel/usuarios_funcionalidades.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="852">
   <si>
     <t>clave</t>
   </si>
@@ -2539,6 +2539,42 @@
   </si>
   <si>
     <t>FERRETERIA D3</t>
+  </si>
+  <si>
+    <t>LOS PRIMOS FERRETERIA</t>
+  </si>
+  <si>
+    <t>FERRETERIA JUAN</t>
+  </si>
+  <si>
+    <t>FERRETERIA HUMBERTO</t>
+  </si>
+  <si>
+    <t>POLIRUBRO ROCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   FERRETERIA FACU</t>
+  </si>
+  <si>
+    <t>FERRETERIA BECO</t>
+  </si>
+  <si>
+    <t>GRAMA COMERCIAL</t>
+  </si>
+  <si>
+    <t>FERRETERIA SANTA ANG</t>
+  </si>
+  <si>
+    <t>CORRALON MIMA</t>
+  </si>
+  <si>
+    <t>BENITO SOSA FERRETER</t>
+  </si>
+  <si>
+    <t>SPIRO EDUARDO FERRET</t>
+  </si>
+  <si>
+    <t>EL POCHOLO FERRETERI</t>
   </si>
 </sst>
 </file>
@@ -2859,7 +2895,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G421"/>
+  <dimension ref="A1:G446"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -8766,6 +8802,356 @@
         <v>10</v>
       </c>
     </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A422" s="1">
+        <v>61007</v>
+      </c>
+      <c r="B422" t="s">
+        <v>840</v>
+      </c>
+      <c r="C422">
+        <v>61007</v>
+      </c>
+      <c r="E422" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A423">
+        <v>1043</v>
+      </c>
+      <c r="B423" t="s">
+        <v>599</v>
+      </c>
+      <c r="C423">
+        <v>1043</v>
+      </c>
+      <c r="E423" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A424">
+        <v>20340</v>
+      </c>
+      <c r="B424" t="s">
+        <v>401</v>
+      </c>
+      <c r="C424">
+        <v>20340</v>
+      </c>
+      <c r="E424" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A425">
+        <v>40146</v>
+      </c>
+      <c r="B425" t="s">
+        <v>691</v>
+      </c>
+      <c r="C425">
+        <v>40146</v>
+      </c>
+      <c r="E425" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A426">
+        <v>60260</v>
+      </c>
+      <c r="B426" t="s">
+        <v>841</v>
+      </c>
+      <c r="C426">
+        <v>60260</v>
+      </c>
+      <c r="E426" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A427">
+        <v>1017</v>
+      </c>
+      <c r="B427" t="s">
+        <v>87</v>
+      </c>
+      <c r="C427">
+        <v>1017</v>
+      </c>
+      <c r="E427" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A428">
+        <v>60300</v>
+      </c>
+      <c r="B428" t="s">
+        <v>842</v>
+      </c>
+      <c r="C428">
+        <v>60300</v>
+      </c>
+      <c r="E428" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A429">
+        <v>20191</v>
+      </c>
+      <c r="B429" t="s">
+        <v>738</v>
+      </c>
+      <c r="C429">
+        <v>20191</v>
+      </c>
+      <c r="E429" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A430">
+        <v>20399</v>
+      </c>
+      <c r="B430" t="s">
+        <v>843</v>
+      </c>
+      <c r="C430">
+        <v>20399</v>
+      </c>
+      <c r="E430" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A431">
+        <v>60240</v>
+      </c>
+      <c r="B431" t="s">
+        <v>844</v>
+      </c>
+      <c r="C431">
+        <v>60240</v>
+      </c>
+      <c r="E431" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A432">
+        <v>60244</v>
+      </c>
+      <c r="B432" t="s">
+        <v>758</v>
+      </c>
+      <c r="C432">
+        <v>60244</v>
+      </c>
+      <c r="E432" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A433">
+        <v>60248</v>
+      </c>
+      <c r="B433" t="s">
+        <v>845</v>
+      </c>
+      <c r="C433">
+        <v>60248</v>
+      </c>
+      <c r="E433" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A434">
+        <v>60288</v>
+      </c>
+      <c r="B434" t="s">
+        <v>447</v>
+      </c>
+      <c r="C434">
+        <v>60288</v>
+      </c>
+      <c r="E434" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A435">
+        <v>90714</v>
+      </c>
+      <c r="B435" t="s">
+        <v>846</v>
+      </c>
+      <c r="C435">
+        <v>90714</v>
+      </c>
+      <c r="E435" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A436">
+        <v>1014</v>
+      </c>
+      <c r="B436" t="s">
+        <v>806</v>
+      </c>
+      <c r="C436">
+        <v>1014</v>
+      </c>
+      <c r="E436" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A437">
+        <v>1016</v>
+      </c>
+      <c r="B437" t="s">
+        <v>327</v>
+      </c>
+      <c r="C437">
+        <v>1016</v>
+      </c>
+      <c r="E437" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A438">
+        <v>60301</v>
+      </c>
+      <c r="B438" t="s">
+        <v>847</v>
+      </c>
+      <c r="C438">
+        <v>60301</v>
+      </c>
+      <c r="E438" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A439">
+        <v>1041</v>
+      </c>
+      <c r="B439" t="s">
+        <v>565</v>
+      </c>
+      <c r="C439">
+        <v>1041</v>
+      </c>
+      <c r="E439" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A440">
+        <v>971</v>
+      </c>
+      <c r="B440" t="s">
+        <v>848</v>
+      </c>
+      <c r="C440">
+        <v>971</v>
+      </c>
+      <c r="E440" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A441">
+        <v>50610</v>
+      </c>
+      <c r="B441" t="s">
+        <v>770</v>
+      </c>
+      <c r="C441">
+        <v>50610</v>
+      </c>
+      <c r="E441" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A442">
+        <v>943</v>
+      </c>
+      <c r="B442" t="s">
+        <v>849</v>
+      </c>
+      <c r="C442">
+        <v>943</v>
+      </c>
+      <c r="E442" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A443">
+        <v>20306</v>
+      </c>
+      <c r="B443" t="s">
+        <v>850</v>
+      </c>
+      <c r="C443">
+        <v>20306</v>
+      </c>
+      <c r="E443" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A444">
+        <v>90630</v>
+      </c>
+      <c r="B444" t="s">
+        <v>421</v>
+      </c>
+      <c r="C444">
+        <v>90630</v>
+      </c>
+      <c r="E444" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A445">
+        <v>1047</v>
+      </c>
+      <c r="B445" t="s">
+        <v>851</v>
+      </c>
+      <c r="C445">
+        <v>1047</v>
+      </c>
+      <c r="E445" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A446">
+        <v>20398</v>
+      </c>
+      <c r="B446" t="s">
+        <v>768</v>
+      </c>
+      <c r="C446">
+        <v>20398</v>
+      </c>
+      <c r="E446" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/excel/usuarios_funcionalidades.xlsx
+++ b/excel/usuarios_funcionalidades.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Usuarios" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Usuarios!$A$1:$G$446</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -19,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="853">
   <si>
     <t>clave</t>
   </si>
@@ -2575,6 +2578,9 @@
   </si>
   <si>
     <t>EL POCHOLO FERRETERI</t>
+  </si>
+  <si>
+    <t>FERRIYAN 2 FERRETERI</t>
   </si>
 </sst>
 </file>
@@ -2895,7 +2901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G446"/>
+  <dimension ref="A1:G447"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -9152,7 +9158,22 @@
         <v>10</v>
       </c>
     </row>
+    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A447">
+        <v>61001</v>
+      </c>
+      <c r="B447" t="s">
+        <v>852</v>
+      </c>
+      <c r="C447">
+        <v>61001</v>
+      </c>
+      <c r="E447" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:G446"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/excel/usuarios_funcionalidades.xlsx
+++ b/excel/usuarios_funcionalidades.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1712" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="853">
   <si>
     <t>clave</t>
   </si>
@@ -2575,6 +2575,9 @@
   </si>
   <si>
     <t>EL POCHOLO FERRETERI</t>
+  </si>
+  <si>
+    <t>FERRETERIA LUCKA</t>
   </si>
 </sst>
 </file>
@@ -2895,7 +2898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G446"/>
+  <dimension ref="A1:G447"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -9152,6 +9155,20 @@
         <v>10</v>
       </c>
     </row>
+    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A447">
+        <v>60305</v>
+      </c>
+      <c r="B447" t="s">
+        <v>852</v>
+      </c>
+      <c r="C447">
+        <v>60305</v>
+      </c>
+      <c r="E447" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/excel/usuarios_funcionalidades.xlsx
+++ b/excel/usuarios_funcionalidades.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1716" uniqueCount="854">
   <si>
     <t>clave</t>
   </si>
@@ -2578,6 +2578,9 @@
   </si>
   <si>
     <t>FERRETERIA LUCKA</t>
+  </si>
+  <si>
+    <t>FERRETERIA OROÑO</t>
   </si>
 </sst>
 </file>
@@ -2898,7 +2901,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G447"/>
+  <dimension ref="A1:G448"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -9169,6 +9172,20 @@
         <v>10</v>
       </c>
     </row>
+    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A448">
+        <v>1051</v>
+      </c>
+      <c r="B448" t="s">
+        <v>853</v>
+      </c>
+      <c r="C448">
+        <v>1051</v>
+      </c>
+      <c r="E448" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/excel/usuarios_funcionalidades.xlsx
+++ b/excel/usuarios_funcionalidades.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1716" uniqueCount="854">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="855">
   <si>
     <t>clave</t>
   </si>
@@ -2581,6 +2581,9 @@
   </si>
   <si>
     <t>FERRETERIA OROÑO</t>
+  </si>
+  <si>
+    <t>FERRETERIA LORENA</t>
   </si>
 </sst>
 </file>
@@ -2901,7 +2904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G448"/>
+  <dimension ref="A1:G449"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -9186,6 +9189,20 @@
         <v>10</v>
       </c>
     </row>
+    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A449">
+        <v>60247</v>
+      </c>
+      <c r="B449" t="s">
+        <v>854</v>
+      </c>
+      <c r="C449">
+        <v>60247</v>
+      </c>
+      <c r="E449" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/excel/usuarios_funcionalidades.xlsx
+++ b/excel/usuarios_funcionalidades.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1718" uniqueCount="855">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="858">
   <si>
     <t>clave</t>
   </si>
@@ -2584,6 +2584,15 @@
   </si>
   <si>
     <t>FERRETERIA LORENA</t>
+  </si>
+  <si>
+    <t>MATIAS OFICINA</t>
+  </si>
+  <si>
+    <t>JOCO OFICINA</t>
+  </si>
+  <si>
+    <t>oficina</t>
   </si>
 </sst>
 </file>
@@ -2904,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G449"/>
+  <dimension ref="A1:G451"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -9203,6 +9212,34 @@
         <v>10</v>
       </c>
     </row>
+    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A450">
+        <v>1987</v>
+      </c>
+      <c r="B450" t="s">
+        <v>855</v>
+      </c>
+      <c r="C450">
+        <v>1987</v>
+      </c>
+      <c r="E450" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A451">
+        <v>1988</v>
+      </c>
+      <c r="B451" t="s">
+        <v>856</v>
+      </c>
+      <c r="C451">
+        <v>1988</v>
+      </c>
+      <c r="E451" t="s">
+        <v>857</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/excel/usuarios_funcionalidades.xlsx
+++ b/excel/usuarios_funcionalidades.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="Usuarios" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="860">
   <si>
     <t>clave</t>
   </si>
@@ -2593,12 +2593,18 @@
   </si>
   <si>
     <t>oficina</t>
+  </si>
+  <si>
+    <t>FERRETERIA RyV</t>
+  </si>
+  <si>
+    <t>FERRETERIA A y J</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2913,7 +2919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G451"/>
+  <dimension ref="A1:G453"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -9240,6 +9246,34 @@
         <v>857</v>
       </c>
     </row>
+    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A452">
+        <v>60308</v>
+      </c>
+      <c r="B452" t="s">
+        <v>858</v>
+      </c>
+      <c r="C452">
+        <v>60308</v>
+      </c>
+      <c r="E452" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A453">
+        <v>60306</v>
+      </c>
+      <c r="B453" t="s">
+        <v>859</v>
+      </c>
+      <c r="C453">
+        <v>60306</v>
+      </c>
+      <c r="E453" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/excel/usuarios_funcionalidades.xlsx
+++ b/excel/usuarios_funcionalidades.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="861">
   <si>
     <t>clave</t>
   </si>
@@ -2599,6 +2599,9 @@
   </si>
   <si>
     <t>FERRETERIA A y J</t>
+  </si>
+  <si>
+    <t>FERRETERIA CLAY</t>
   </si>
 </sst>
 </file>
@@ -2919,7 +2922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G453"/>
+  <dimension ref="A1:G454"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -9274,6 +9277,20 @@
         <v>10</v>
       </c>
     </row>
+    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A454">
+        <v>20192</v>
+      </c>
+      <c r="B454" t="s">
+        <v>860</v>
+      </c>
+      <c r="C454">
+        <v>20192</v>
+      </c>
+      <c r="E454" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/excel/usuarios_funcionalidades.xlsx
+++ b/excel/usuarios_funcionalidades.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1728" uniqueCount="861">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="862">
   <si>
     <t>clave</t>
   </si>
@@ -2602,6 +2602,9 @@
   </si>
   <si>
     <t>FERRETERIA CLAY</t>
+  </si>
+  <si>
+    <t>DEPO P.BAJA</t>
   </si>
 </sst>
 </file>
@@ -2922,7 +2925,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G454"/>
+  <dimension ref="A1:G455"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -9291,6 +9294,20 @@
         <v>10</v>
       </c>
     </row>
+    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A455">
+        <v>1989</v>
+      </c>
+      <c r="B455" t="s">
+        <v>861</v>
+      </c>
+      <c r="C455">
+        <v>1989</v>
+      </c>
+      <c r="E455" t="s">
+        <v>857</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/excel/usuarios_funcionalidades.xlsx
+++ b/excel/usuarios_funcionalidades.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="865">
   <si>
     <t>clave</t>
   </si>
@@ -2605,6 +2605,15 @@
   </si>
   <si>
     <t>DEPO P.BAJA</t>
+  </si>
+  <si>
+    <t>F. RAUCH ADRIAN</t>
+  </si>
+  <si>
+    <t>F. VALVERDE</t>
+  </si>
+  <si>
+    <t>F. ANIBAL</t>
   </si>
 </sst>
 </file>
@@ -2925,7 +2934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G455"/>
+  <dimension ref="A1:G458"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -9308,6 +9317,48 @@
         <v>857</v>
       </c>
     </row>
+    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A456">
+        <v>50226</v>
+      </c>
+      <c r="B456" t="s">
+        <v>862</v>
+      </c>
+      <c r="C456">
+        <v>50226</v>
+      </c>
+      <c r="E456" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A457">
+        <v>70117</v>
+      </c>
+      <c r="B457" t="s">
+        <v>864</v>
+      </c>
+      <c r="C457">
+        <v>70117</v>
+      </c>
+      <c r="E457" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A458">
+        <v>70118</v>
+      </c>
+      <c r="B458" t="s">
+        <v>863</v>
+      </c>
+      <c r="C458">
+        <v>70118</v>
+      </c>
+      <c r="E458" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/excel/usuarios_funcionalidades.xlsx
+++ b/excel/usuarios_funcionalidades.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="867">
   <si>
     <t>clave</t>
   </si>
@@ -2614,12 +2614,18 @@
   </si>
   <si>
     <t>F. ANIBAL</t>
+  </si>
+  <si>
+    <t>FERRETERIA SENEGAL</t>
+  </si>
+  <si>
+    <t>CONSUMIDOR FINAL 4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2934,7 +2940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G458"/>
+  <dimension ref="A1:G460"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -9359,6 +9365,34 @@
         <v>10</v>
       </c>
     </row>
+    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A459">
+        <v>20307</v>
+      </c>
+      <c r="B459" t="s">
+        <v>865</v>
+      </c>
+      <c r="C459">
+        <v>20307</v>
+      </c>
+      <c r="E459" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A460">
+        <v>4</v>
+      </c>
+      <c r="B460" t="s">
+        <v>866</v>
+      </c>
+      <c r="C460">
+        <v>4</v>
+      </c>
+      <c r="E460" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/excel/usuarios_funcionalidades.xlsx
+++ b/excel/usuarios_funcionalidades.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
@@ -2616,16 +2616,16 @@
     <t>F. ANIBAL</t>
   </si>
   <si>
-    <t>FERRETERIA SENEGAL</t>
-  </si>
-  <si>
     <t>CONSUMIDOR FINAL 4</t>
+  </si>
+  <si>
+    <t>FERRETERIA SENGUEL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -9370,7 +9370,7 @@
         <v>20307</v>
       </c>
       <c r="B459" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C459">
         <v>20307</v>
@@ -9384,7 +9384,7 @@
         <v>4</v>
       </c>
       <c r="B460" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C460">
         <v>4</v>

--- a/excel/usuarios_funcionalidades.xlsx
+++ b/excel/usuarios_funcionalidades.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="868">
   <si>
     <t>clave</t>
   </si>
@@ -2620,12 +2620,15 @@
   </si>
   <si>
     <t>FERRETERIA SENGUEL</t>
+  </si>
+  <si>
+    <t>CLIENTE PRUEBA- NO FACTURAR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2940,7 +2943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G460"/>
+  <dimension ref="A1:G461"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -9393,6 +9396,20 @@
         <v>10</v>
       </c>
     </row>
+    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A461">
+        <v>7</v>
+      </c>
+      <c r="B461" t="s">
+        <v>867</v>
+      </c>
+      <c r="C461">
+        <v>7</v>
+      </c>
+      <c r="E461" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/excel/usuarios_funcionalidades.xlsx
+++ b/excel/usuarios_funcionalidades.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1742" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="869">
   <si>
     <t>clave</t>
   </si>
@@ -2623,12 +2623,15 @@
   </si>
   <si>
     <t>CLIENTE PRUEBA- NO FACTURAR</t>
+  </si>
+  <si>
+    <t>CATAN CITY FERRETERI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2943,7 +2946,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G461"/>
+  <dimension ref="A1:G462"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -9410,6 +9413,20 @@
         <v>10</v>
       </c>
     </row>
+    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A462">
+        <v>20325</v>
+      </c>
+      <c r="B462" t="s">
+        <v>868</v>
+      </c>
+      <c r="C462">
+        <v>20325</v>
+      </c>
+      <c r="E462" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/excel/usuarios_funcionalidades.xlsx
+++ b/excel/usuarios_funcionalidades.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="876">
   <si>
     <t>clave</t>
   </si>
@@ -2626,6 +2626,27 @@
   </si>
   <si>
     <t>CATAN CITY FERRETERI</t>
+  </si>
+  <si>
+    <t>FERRETERIA MAESTRO</t>
+  </si>
+  <si>
+    <t>50814</t>
+  </si>
+  <si>
+    <t>CASA PEKY</t>
+  </si>
+  <si>
+    <t>70117</t>
+  </si>
+  <si>
+    <t>FERRETERIA ANIBAL</t>
+  </si>
+  <si>
+    <t>60209</t>
+  </si>
+  <si>
+    <t>DEL PINAR FERRETERIA</t>
   </si>
 </sst>
 </file>
@@ -2946,7 +2967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G462"/>
+  <dimension ref="A1:G466"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
@@ -9427,6 +9448,62 @@
         <v>10</v>
       </c>
     </row>
+    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A463">
+        <v>50836</v>
+      </c>
+      <c r="B463" t="s">
+        <v>869</v>
+      </c>
+      <c r="C463">
+        <v>50836</v>
+      </c>
+      <c r="E463" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>870</v>
+      </c>
+      <c r="B464" t="s">
+        <v>871</v>
+      </c>
+      <c r="C464">
+        <v>50814</v>
+      </c>
+      <c r="E464" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>872</v>
+      </c>
+      <c r="B465" t="s">
+        <v>873</v>
+      </c>
+      <c r="C465">
+        <v>70117</v>
+      </c>
+      <c r="E465" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>874</v>
+      </c>
+      <c r="B466" t="s">
+        <v>875</v>
+      </c>
+      <c r="C466">
+        <v>60209</v>
+      </c>
+      <c r="E466" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
